--- a/pa-temp-fix-system.com/php/export/需要删除来货的.xlsx
+++ b/pa-temp-fix-system.com/php/export/需要删除来货的.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17970"/>
+    <workbookView windowWidth="31770" windowHeight="17970"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
   <si>
     <t>skuId</t>
   </si>
@@ -44,7 +44,7 @@
     <t>delete3</t>
   </si>
   <si>
-    <t>g25112600ux0702</t>
+    <t>g26030400ux0324</t>
   </si>
   <si>
     <t>local</t>
@@ -59,16 +59,10 @@
     <t>来货brand类型</t>
   </si>
   <si>
-    <t>g25120200ux0013</t>
+    <t>g26030400ux0325</t>
   </si>
   <si>
-    <t>g25120200ux0012</t>
-  </si>
-  <si>
-    <t>g25120200ux0858</t>
-  </si>
-  <si>
-    <t>g25120200ux0859</t>
+    <t>g26031100ux0444</t>
   </si>
 </sst>
 </file>
@@ -1223,8 +1217,8 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="18" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.6" customWidth="1"/>
     <col min="2" max="2" width="16.8166666666667" customWidth="1"/>
@@ -1300,40 +1294,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" ht="19.5" spans="1:5">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="19.5" spans="1:5">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
